--- a/workers/duc-auto-chatgpt/v0.1.0/pilot-06/Duc-Auto-ChatGPT-Pilot-06__results__v001.xlsx
+++ b/workers/duc-auto-chatgpt/v0.1.0/pilot-06/Duc-Auto-ChatGPT-Pilot-06__results__v001.xlsx
@@ -759,6 +759,30 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P06-D</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A dark green glass bottle standing on a pale wooden shelf, soft window light.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P06-E</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>One folded white paper boat on a plain light blue surface, gentle shadow.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
